--- a/jogos_2024-09-26.xlsx
+++ b/jogos_2024-09-26.xlsx
@@ -1417,109 +1417,109 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O8" t="n">
         <v>3</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.6</v>
-      </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S8" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X8" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AD8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['55', '82', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI8" t="n">
         <v>1.8</v>
       </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>['49', '51', '69']</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ8" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45561.4375</v>
@@ -1546,20 +1546,20 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>3</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X9" t="n">
         <v>2.9</v>
       </c>
-      <c r="N9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O9" t="n">
+      <c r="Y9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['49', '51', '69']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>3</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>['55', '82', '90+1']</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>2.38</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45561.4375</v>
@@ -1794,29 +1794,29 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Moghayer Al Sarhan</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>6</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.53</v>
       </c>
-      <c r="O11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['41', '50', '61', '85']</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>2.15</v>
+        <v>1.03</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.13</v>
+        <v>2.9</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.25</v>
+        <v>1.29</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45561.5</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.2</v>
+        <v>1.91</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>1.85</v>
+        <v>3.9</v>
       </c>
       <c r="O12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T12" t="n">
         <v>3.6</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC12" t="n">
         <v>2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="AD12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI12" t="n">
         <v>1.62</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['61', '85']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['16']</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>2.22</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>1.63</v>
+        <v>3</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45561.5</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Moghayer Al Sarhan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC13" t="n">
         <v>1.91</v>
       </c>
-      <c r="M13" t="n">
-        <v>3</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2151,20 +2151,20 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41', '50', '61', '85']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>2.15</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.65</v>
+        <v>1.13</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.62</v>
+        <v>3.25</v>
       </c>
       <c r="AJ13" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45561.5</v>
@@ -2181,26 +2181,26 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>4.33</v>
+        <v>1.85</v>
       </c>
       <c r="O14" t="n">
-        <v>1.91</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="S14" t="n">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="T14" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>['61', '85']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.29</v>
+        <v>2.22</v>
       </c>
       <c r="AJ14" t="n">
-        <v>4</v>
+        <v>1.63</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45561.5</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,109 +2449,109 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" t="n">
         <v>2</v>
       </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
       <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="M16" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="O16" t="n">
         <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>3.22</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.39</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>3.96</v>
+        <v>5.35</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['22', '30', '45+4', '68']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['36', '40']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.67</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['16', '39']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['85']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45561.54166666666</v>
@@ -2707,109 +2707,109 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Umm al-Fahm</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O18" t="n">
         <v>2</v>
       </c>
-      <c r="H18" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="P18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD18" t="n">
         <v>2</v>
       </c>
-      <c r="J18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X18" t="n">
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['9', '56', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>3.2</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['31', '45+1']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['7', '21', '27']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.5</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45561.54166666666</v>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Umm al-Fahm</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
         <v>3</v>
       </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['31', '45+1']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['7', '21', '27']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['9', '56', '90+1']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>3.2</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45561.54166666666</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
-        <v>3</v>
-      </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="O20" t="n">
         <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>3.22</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>2.39</v>
       </c>
       <c r="U20" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="V20" t="n">
         <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>5.35</v>
+        <v>3.96</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['16', '39']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
         <v>1.45</v>
       </c>
-      <c r="Z20" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['22', '30', '45+4', '68']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['36', '40']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45561.54166666666</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,20 +3094,20 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Milan II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>SPAL</t>
         </is>
       </c>
       <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
         <v>1</v>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.61</v>
+        <v>2.55</v>
       </c>
       <c r="M21" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="N21" t="n">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="O21" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['67', '85']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['81']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.33</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U21" t="n">
+      <c r="AH21" t="n">
         <v>1.5</v>
       </c>
-      <c r="V21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z21" t="n">
+      <c r="AI21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['89']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>2.6</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45561.5625</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,109 +3223,109 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Milan II</t>
+          <t>Clodiense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SPAL</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>2</v>
       </c>
       <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="N22" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S22" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="T22" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="W22" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="X22" t="n">
-        <v>2.83</v>
+        <v>2.3</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="Z22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA22" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['67', '85']</t>
+          <t>['1', '4']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>['44', '67']</t>
         </is>
       </c>
       <c r="AG22" t="n">
         <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45561.5625</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3370,7 +3370,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="M23" t="n">
         <v>2.88</v>
       </c>
       <c r="N23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
         <v>3.25</v>
       </c>
-      <c r="O23" t="n">
-        <v>3</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.75</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T23" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="U23" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="V23" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W23" t="n">
         <v>1.4</v>
       </c>
       <c r="X23" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.28</v>
+        <v>3.86</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AC23" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45561.5625</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Clodiense</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.75</v>
+        <v>1.61</v>
       </c>
       <c r="M24" t="n">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>2.75</v>
+        <v>4.33</v>
       </c>
       <c r="O24" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="P24" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="R24" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="T24" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="V24" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AI24" t="n">
         <v>1.53</v>
       </c>
-      <c r="X24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['1', '4']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['44', '67']</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45561.5625</v>
@@ -3610,22 +3610,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.52</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.22</v>
+        <v>2.88</v>
       </c>
       <c r="N25" t="n">
-        <v>1.94</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['8', '50']</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['34', '73']</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45561.5625</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,109 +3739,109 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
         <v>1</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.75</v>
+        <v>3.52</v>
       </c>
       <c r="M26" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="N26" t="n">
-        <v>2.63</v>
+        <v>1.94</v>
       </c>
       <c r="O26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['47']</t>
+          <t>['8', '50']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['34', '73']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45561.5625</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M27" t="n">
         <v>3</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.2</v>
-      </c>
       <c r="N27" t="n">
-        <v>2.37</v>
+        <v>3.9</v>
       </c>
       <c r="O27" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="P27" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S27" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['24']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>3.25</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['9']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>['45+3']</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45561.58333333334</v>
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
         <v>1</v>
       </c>
-      <c r="H28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4032,74 +4032,74 @@
         <v>2.5</v>
       </c>
       <c r="O28" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="V28" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="X28" t="n">
-        <v>3.35</v>
+        <v>5.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AD28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['7', '64']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['13', '40']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>2</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['66']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>['21']</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45561.58333333334</v>
@@ -4116,32 +4116,32 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P29" t="n">
         <v>2.1</v>
       </c>
-      <c r="O29" t="n">
-        <v>4</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S29" t="n">
         <v>2.75</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.4</v>
       </c>
       <c r="V29" t="n">
         <v>1.06</v>
       </c>
       <c r="W29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB29" t="n">
         <v>1.3</v>
       </c>
-      <c r="X29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y29" t="n">
+      <c r="AC29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI29" t="n">
         <v>1.83</v>
       </c>
-      <c r="Z29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>['45+1']</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>['45+6', '63']</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AJ29" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45561.58333333334</v>
@@ -4245,35 +4245,35 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.55</v>
+        <v>3.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="O30" t="n">
-        <v>2.38</v>
+        <v>4</v>
       </c>
       <c r="P30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>['45+1']</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>['45+6', '63']</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI30" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>['77']</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ30" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45561.58333333334</v>
@@ -4374,35 +4374,35 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N31" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="O31" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="P31" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="R31" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="T31" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="U31" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="V31" t="n">
         <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X31" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['4', '7', '27', '90+9']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['42', '59']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45561.58333333334</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,109 +4513,109 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N32" t="n">
         <v>3.9</v>
       </c>
       <c r="O32" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X32" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA32" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S32" t="n">
+      <c r="AB32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['4', '7', '27', '90+9']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>['42', '59']</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH32" t="n">
         <v>2.25</v>
       </c>
-      <c r="T32" t="n">
-        <v>4</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>['24']</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AI32" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AJ32" t="n">
-        <v>3.25</v>
+        <v>2.44</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45561.58333333334</v>
@@ -4761,35 +4761,35 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Al Khor</t>
         </is>
       </c>
       <c r="G34" t="n">
+        <v>3</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
         <v>2</v>
       </c>
-      <c r="H34" t="n">
-        <v>2</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1</v>
-      </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4797,25 +4797,25 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="M34" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>5.25</v>
       </c>
       <c r="O34" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="P34" t="n">
         <v>2.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S34" t="n">
         <v>3.5</v>
@@ -4830,7 +4830,7 @@
         <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X34" t="n">
         <v>5.5</v>
@@ -4848,32 +4848,32 @@
         <v>1.57</v>
       </c>
       <c r="AC34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>['21', '45+2', '62']</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI34" t="n">
         <v>1.44</v>
       </c>
-      <c r="AD34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>['7', '64']</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>['13', '40']</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ34" t="n">
-        <v>2</v>
+        <v>2.95</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45561.58333333334</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Khor</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>3</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R35" t="n">
         <v>1.44</v>
       </c>
-      <c r="M35" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="N35" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="O35" t="n">
+      <c r="S35" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X35" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC35" t="n">
         <v>1.91</v>
       </c>
-      <c r="P35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X35" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AD35" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['21', '45+2', '62']</t>
+          <t>['9']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.09</v>
+        <v>1.55</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.6</v>
+        <v>1.36</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.95</v>
+        <v>1.8</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45561.58333333334</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,25 +5287,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G38" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" t="n">
         <v>1</v>
       </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.1</v>
+        <v>1.73</v>
       </c>
       <c r="M38" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N38" t="n">
-        <v>1.85</v>
+        <v>4.33</v>
       </c>
       <c r="O38" t="n">
-        <v>4.5</v>
+        <v>2.38</v>
       </c>
       <c r="P38" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="R38" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S38" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T38" t="n">
         <v>3.25</v>
       </c>
       <c r="U38" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V38" t="n">
         <v>1.08</v>
       </c>
       <c r="W38" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="X38" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>['21', '59']</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>['8', '33', '70']</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>2.88</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>['81']</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.57</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45561.65625</v>
@@ -5416,81 +5416,81 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3</v>
+      </c>
+      <c r="J39" t="n">
         <v>1</v>
       </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="M39" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N39" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="O39" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="P39" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="R39" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S39" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="T39" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U39" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V39" t="n">
         <v>1.07</v>
       </c>
       <c r="W39" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="X39" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AA39" t="n">
-        <v>4.2</v>
+        <v>4.42</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC39" t="n">
         <v>2.1</v>
@@ -5500,25 +5500,25 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22', '27', '45']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>['41', '88']</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45561.65625</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,25 +5674,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G41" t="n">
         <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="M41" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="O41" t="n">
-        <v>2.38</v>
+        <v>3.02</v>
       </c>
       <c r="P41" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.75</v>
+        <v>2.88</v>
       </c>
       <c r="R41" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="S41" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="T41" t="n">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="U41" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="V41" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W41" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="X41" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="Y41" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.8</v>
+        <v>2.55</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.65</v>
+        <v>2.25</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.19</v>
+        <v>1.57</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.8</v>
+        <v>2.65</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['21', '59']</t>
+          <t>['77', '90+4']</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>['8', '33', '70']</t>
+          <t>['90+8']</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.2</v>
+        <v>1.54</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.5</v>
+        <v>1.94</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.88</v>
+        <v>1.89</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45561.65625</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,109 +5803,109 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P42" t="n">
         <v>2</v>
       </c>
-      <c r="H42" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
+      <c r="Q42" t="n">
         <v>2.5</v>
       </c>
-      <c r="M42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N42" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O42" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X42" t="n">
         <v>2.88</v>
       </c>
-      <c r="R42" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X42" t="n">
-        <v>4.9</v>
-      </c>
       <c r="Y42" t="n">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.25</v>
+        <v>4.5</v>
       </c>
       <c r="AB42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>['81']</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AJ42" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>['77', '90+4']</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>['90+8']</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.89</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45561.65625</v>
@@ -5932,81 +5932,81 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M43" t="n">
         <v>3</v>
       </c>
-      <c r="H43" t="n">
-        <v>2</v>
-      </c>
-      <c r="I43" t="n">
-        <v>3</v>
-      </c>
-      <c r="J43" t="n">
-        <v>1</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M43" t="n">
-        <v>2.8</v>
-      </c>
       <c r="N43" t="n">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="O43" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="P43" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="R43" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="S43" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="T43" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U43" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V43" t="n">
         <v>1.07</v>
       </c>
       <c r="W43" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="X43" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AA43" t="n">
-        <v>4.42</v>
+        <v>4.2</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC43" t="n">
         <v>2.1</v>
@@ -6016,25 +6016,25 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['22', '27', '45']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['41', '88']</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AJ43" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45561.65625</v>
